--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G411"/>
+  <dimension ref="A1:G413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11533,6 +11533,60 @@
         <v>341.3</v>
       </c>
       <c r="G411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="C412" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="D412" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="E412" t="n">
+        <v>338.05</v>
+      </c>
+      <c r="F412" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>340.37</v>
+      </c>
+      <c r="C413" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="D413" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="E413" t="n">
+        <v>337.88</v>
+      </c>
+      <c r="F413" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="G413" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11549,7 +11603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15852,6 +15906,26 @@
       </c>
       <c r="B430" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -16020,28 +16094,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2890495839342771</v>
+        <v>-0.2891003420853999</v>
       </c>
       <c r="J2" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K2" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2755957651009789</v>
+        <v>0.2777807375873335</v>
       </c>
       <c r="M2" t="n">
-        <v>2.750258034750566</v>
+        <v>2.737361884356151</v>
       </c>
       <c r="N2" t="n">
-        <v>12.46552412965384</v>
+        <v>12.40506035610122</v>
       </c>
       <c r="O2" t="n">
-        <v>3.530654915118984</v>
+        <v>3.522081821324034</v>
       </c>
       <c r="P2" t="n">
-        <v>348.2808674654689</v>
+        <v>348.281408121191</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16098,28 +16172,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3044898675955911</v>
+        <v>-0.3040142066383341</v>
       </c>
       <c r="J3" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K3" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4491721019515247</v>
+        <v>0.4509674661095722</v>
       </c>
       <c r="M3" t="n">
-        <v>1.857917964090449</v>
+        <v>1.850885677816346</v>
       </c>
       <c r="N3" t="n">
-        <v>6.45366250377472</v>
+        <v>6.423553647099211</v>
       </c>
       <c r="O3" t="n">
-        <v>2.540405972236469</v>
+        <v>2.534473051168469</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1444302625319</v>
+        <v>344.1393710177471</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16176,28 +16250,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1194081027123192</v>
+        <v>-0.1232408150239688</v>
       </c>
       <c r="J4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09526475314882898</v>
+        <v>0.1008794664094205</v>
       </c>
       <c r="M4" t="n">
-        <v>2.074121044912338</v>
+        <v>2.085131047458578</v>
       </c>
       <c r="N4" t="n">
-        <v>7.686245733812839</v>
+        <v>7.727855502736808</v>
       </c>
       <c r="O4" t="n">
-        <v>2.772407930628687</v>
+        <v>2.779902067112582</v>
       </c>
       <c r="P4" t="n">
-        <v>350.429063608492</v>
+        <v>350.4698266371991</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16254,28 +16328,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01787318380629142</v>
+        <v>-0.02202374799989033</v>
       </c>
       <c r="J5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002166226316414943</v>
+        <v>0.003283795298732239</v>
       </c>
       <c r="M5" t="n">
-        <v>2.208712313376867</v>
+        <v>2.217504688453514</v>
       </c>
       <c r="N5" t="n">
-        <v>8.352483394769067</v>
+        <v>8.404514494527437</v>
       </c>
       <c r="O5" t="n">
-        <v>2.890066330513725</v>
+        <v>2.899054068921005</v>
       </c>
       <c r="P5" t="n">
-        <v>342.8464316109254</v>
+        <v>342.8905763347354</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16332,28 +16406,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2660521474091023</v>
+        <v>-0.2683461967607643</v>
       </c>
       <c r="J6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3084852190000253</v>
+        <v>0.3137478929615174</v>
       </c>
       <c r="M6" t="n">
-        <v>2.454660790232215</v>
+        <v>2.452479093475925</v>
       </c>
       <c r="N6" t="n">
-        <v>9.006541423725572</v>
+        <v>8.991424291133697</v>
       </c>
       <c r="O6" t="n">
-        <v>3.001090039256665</v>
+        <v>2.998570374550795</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4092721752365</v>
+        <v>350.4336733951498</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16391,7 +16465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G411"/>
+  <dimension ref="A1:G413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31601,6 +31675,80 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-42.871463357335195,173.3102947441116</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-42.87210187387669,173.3100598716592</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-42.872763419952115,173.30999064929176</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-42.87342656262868,173.30992589461036</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-42.87408251160197,173.31001926334872</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-42.871463027709005,173.3102925864018</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-42.87210195651338,173.3100604734221</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-42.87276345687222,173.30999125939795</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-42.87342661217716,173.30992381430863</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-42.87408282695472,173.3100126657148</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11587,6 +11587,87 @@
         <v>340.56</v>
       </c>
       <c r="G413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="C414" t="n">
+        <v>337.02</v>
+      </c>
+      <c r="D414" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="E414" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="F414" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>340.82</v>
+      </c>
+      <c r="C415" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="D415" t="n">
+        <v>343.74</v>
+      </c>
+      <c r="E415" t="n">
+        <v>338.06</v>
+      </c>
+      <c r="F415" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="C416" t="n">
+        <v>337.65</v>
+      </c>
+      <c r="D416" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="E416" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="F416" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="G416" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11603,7 +11684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B432"/>
+  <dimension ref="A1:B435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15926,6 +16007,36 @@
       </c>
       <c r="B432" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -16094,28 +16205,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2891003420853999</v>
+        <v>-0.2886678343624843</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2777807375873335</v>
+        <v>0.2803164251500797</v>
       </c>
       <c r="M2" t="n">
-        <v>2.737361884356151</v>
+        <v>2.719394265308524</v>
       </c>
       <c r="N2" t="n">
-        <v>12.40506035610122</v>
+        <v>12.3162001556447</v>
       </c>
       <c r="O2" t="n">
-        <v>3.522081821324034</v>
+        <v>3.50944442264651</v>
       </c>
       <c r="P2" t="n">
-        <v>348.281408121191</v>
+        <v>348.2767912262232</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16172,28 +16283,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3040142066383341</v>
+        <v>-0.3020952432650893</v>
       </c>
       <c r="J3" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4509674661095722</v>
+        <v>0.4511704989594209</v>
       </c>
       <c r="M3" t="n">
-        <v>1.850885677816346</v>
+        <v>1.84542577788875</v>
       </c>
       <c r="N3" t="n">
-        <v>6.423553647099211</v>
+        <v>6.391038481358348</v>
       </c>
       <c r="O3" t="n">
-        <v>2.534473051168469</v>
+        <v>2.528050332046091</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1393710177471</v>
+        <v>344.1188923976492</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16250,28 +16361,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1232408150239688</v>
+        <v>-0.12773661752095</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K4" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1008794664094205</v>
+        <v>0.1081281042705832</v>
       </c>
       <c r="M4" t="n">
-        <v>2.085131047458578</v>
+        <v>2.095540633327163</v>
       </c>
       <c r="N4" t="n">
-        <v>7.727855502736808</v>
+        <v>7.747857394855909</v>
       </c>
       <c r="O4" t="n">
-        <v>2.779902067112582</v>
+        <v>2.783497331569748</v>
       </c>
       <c r="P4" t="n">
-        <v>350.4698266371991</v>
+        <v>350.5177840212101</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16328,28 +16439,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02202374799989033</v>
+        <v>-0.02758578628849632</v>
       </c>
       <c r="J5" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K5" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003283795298732239</v>
+        <v>0.005152991434018483</v>
       </c>
       <c r="M5" t="n">
-        <v>2.217504688453514</v>
+        <v>2.228120421351761</v>
       </c>
       <c r="N5" t="n">
-        <v>8.404514494527437</v>
+        <v>8.457743646376795</v>
       </c>
       <c r="O5" t="n">
-        <v>2.899054068921005</v>
+        <v>2.908220013406275</v>
       </c>
       <c r="P5" t="n">
-        <v>342.8905763347354</v>
+        <v>342.9499124777271</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16406,28 +16517,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2683461967607643</v>
+        <v>-0.2713548912859071</v>
       </c>
       <c r="J6" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3137478929615174</v>
+        <v>0.3211440241839477</v>
       </c>
       <c r="M6" t="n">
-        <v>2.452479093475925</v>
+        <v>2.447543866304352</v>
       </c>
       <c r="N6" t="n">
-        <v>8.991424291133697</v>
+        <v>8.960660309376713</v>
       </c>
       <c r="O6" t="n">
-        <v>2.998570374550795</v>
+        <v>2.99343620432718</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4336733951498</v>
+        <v>350.4657667842714</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16465,7 +16576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31749,6 +31860,117 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-42.87146352214828,173.31029582296648</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-42.872102832462154,173.31006685210895</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-42.872763597168564,173.30999357780144</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-42.873426583031005,173.30992503801554</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-42.874082780235824,173.31001364314204</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-42.8714638517744,173.3102979806763</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-42.87210331175473,173.31007034233386</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-42.87276387037709,173.30999809258716</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-42.87342655971407,173.30992601698102</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-42.874082634239194,173.3100166976022</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-42.8714640898377,173.31029953902225</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-42.87210387368383,173.3100744343218</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-42.87276453493763,173.3100090744986</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-42.87342632654423,173.30993580663602</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-42.87408222544822,173.31002525009052</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G416"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11668,6 +11668,33 @@
         <v>341.59</v>
       </c>
       <c r="G416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>340.82</v>
+      </c>
+      <c r="C417" t="n">
+        <v>337.87</v>
+      </c>
+      <c r="D417" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="E417" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="F417" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="G417" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11684,7 +11711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B435"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16037,6 +16064,16 @@
       </c>
       <c r="B435" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -16205,28 +16242,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2886678343624843</v>
+        <v>-0.2885058773211436</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2803164251500797</v>
+        <v>0.2811333931159379</v>
       </c>
       <c r="M2" t="n">
-        <v>2.719394265308524</v>
+        <v>2.7135323197543</v>
       </c>
       <c r="N2" t="n">
-        <v>12.3162001556447</v>
+        <v>12.28688479171704</v>
       </c>
       <c r="O2" t="n">
-        <v>3.50944442264651</v>
+        <v>3.505265295482931</v>
       </c>
       <c r="P2" t="n">
-        <v>348.2767912262232</v>
+        <v>348.2750572111683</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16283,28 +16320,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3020952432650893</v>
+        <v>-0.301206508001494</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4511704989594209</v>
+        <v>0.450657175458826</v>
       </c>
       <c r="M3" t="n">
-        <v>1.84542577788875</v>
+        <v>1.844653418763472</v>
       </c>
       <c r="N3" t="n">
-        <v>6.391038481358348</v>
+        <v>6.384434692794034</v>
       </c>
       <c r="O3" t="n">
-        <v>2.528050332046091</v>
+        <v>2.526743891413223</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1188923976492</v>
+        <v>344.1093770328698</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16361,28 +16398,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.12773661752095</v>
+        <v>-0.1285375497191344</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1081281042705832</v>
+        <v>0.1097563309492049</v>
       </c>
       <c r="M4" t="n">
-        <v>2.095540633327163</v>
+        <v>2.095108306820396</v>
       </c>
       <c r="N4" t="n">
-        <v>7.747857394855909</v>
+        <v>7.736346761616378</v>
       </c>
       <c r="O4" t="n">
-        <v>2.783497331569748</v>
+        <v>2.781428906446537</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5177840212101</v>
+        <v>350.526359310547</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16439,28 +16476,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02758578628849632</v>
+        <v>-0.02908804219794266</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005152991434018483</v>
+        <v>0.005738923226575987</v>
       </c>
       <c r="M5" t="n">
-        <v>2.228120421351761</v>
+        <v>2.229910892243509</v>
       </c>
       <c r="N5" t="n">
-        <v>8.457743646376795</v>
+        <v>8.462439697001328</v>
       </c>
       <c r="O5" t="n">
-        <v>2.908220013406275</v>
+        <v>2.909027276771623</v>
       </c>
       <c r="P5" t="n">
-        <v>342.9499124777271</v>
+        <v>342.9659965846102</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16517,28 +16554,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2713548912859071</v>
+        <v>-0.2721394604775121</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3211440241839477</v>
+        <v>0.3233724394780078</v>
       </c>
       <c r="M6" t="n">
-        <v>2.447543866304352</v>
+        <v>2.444974920643134</v>
       </c>
       <c r="N6" t="n">
-        <v>8.960660309376713</v>
+        <v>8.945946575448186</v>
       </c>
       <c r="O6" t="n">
-        <v>2.99343620432718</v>
+        <v>2.990977528409096</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4657667842714</v>
+        <v>350.4741668808564</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16576,7 +16613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G416"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31971,6 +32008,43 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-42.8714638517744,173.3102979806763</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-42.87210423728492,173.3100770820787</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-42.87276505181732,173.31001761598546</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-42.8734262944833,173.3099371527136</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-42.87408231304634,173.31002341741447</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
